--- a/artfynd/S 4434-2023 artfynd.xlsx
+++ b/artfynd/S 4434-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AZ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61799144</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61798974</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61299996</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61799063</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114785342</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1306,6 +1336,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61798994</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61799319</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1516,6 +1556,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61799306</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1621,6 +1666,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61299974</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1734,6 +1784,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61799110</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1847,6 +1902,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61799123</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1960,6 +2020,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61799392</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2073,6 +2138,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61799418</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2186,6 +2256,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67981939</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2291,6 +2366,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61799427</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2396,6 +2476,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61299941</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2509,6 +2594,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61300016</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2610,6 +2700,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114785379</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2715,6 +2810,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61300060</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2815,6 +2915,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61300192</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2915,6 +3020,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61299945</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3015,6 +3125,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61300021</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3115,6 +3230,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61300047</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3220,6 +3340,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61798561</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3321,6 +3446,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114785438</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3426,6 +3556,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61299957</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3531,6 +3666,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61799016</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3636,6 +3776,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61799405</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3741,6 +3886,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61798950</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3846,6 +3996,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61799435</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3951,6 +4106,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67982372</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4051,6 +4211,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61299960</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4156,6 +4321,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61798547</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4261,6 +4431,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61799037</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4366,6 +4541,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61799448</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4478,6 +4658,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115909171</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4585,6 +4770,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61799723</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4696,6 +4886,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67982297</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4807,6 +5002,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67982316</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4918,6 +5118,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61799177</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5023,6 +5228,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67982269</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5128,6 +5338,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61798580</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5241,6 +5456,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67981918</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5342,6 +5562,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114785340</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5455,6 +5680,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67981824</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5556,6 +5786,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114785432</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5669,6 +5904,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67981889</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5774,6 +6014,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61799617</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5879,6 +6124,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61799634</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5984,6 +6234,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67981829</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6089,6 +6344,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61799571</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6194,6 +6454,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67981899</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6299,6 +6564,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67981878</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6404,6 +6674,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61799476</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6504,6 +6779,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61799652</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6609,8 +6889,71 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61799647</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>